--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_170_R17.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_170_R17.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.5846</v>
+        <v>7.828</v>
       </c>
       <c r="E2" t="n">
-        <v>4.5593</v>
+        <v>4.8699</v>
       </c>
       <c r="F2" t="n">
-        <v>3.0253</v>
+        <v>2.9581</v>
       </c>
       <c r="G2" t="n">
         <v>4.0992</v>
@@ -610,13 +610,13 @@
         <v>2.0876</v>
       </c>
       <c r="S2" t="n">
-        <v>1.6298</v>
+        <v>1.8732</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4876</v>
+        <v>0.7982</v>
       </c>
       <c r="U2" t="n">
-        <v>1.1422</v>
+        <v>1.075</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>E. ULANOVAS</t>
+          <t>M. WRIGHT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.0299</v>
+        <v>6.8123</v>
       </c>
       <c r="E3" t="n">
-        <v>4.6232</v>
+        <v>4.4754</v>
       </c>
       <c r="F3" t="n">
-        <v>2.4068</v>
+        <v>2.3369</v>
       </c>
       <c r="G3" t="n">
-        <v>1.8331</v>
+        <v>4.4692</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.2917</v>
+        <v>3.5725</v>
       </c>
       <c r="I3" t="n">
-        <v>2.1248</v>
+        <v>0.8968</v>
       </c>
       <c r="J3" t="n">
-        <v>1.7657</v>
+        <v>4.2766</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4775</v>
+        <v>3.8483</v>
       </c>
       <c r="L3" t="n">
-        <v>1.2882</v>
+        <v>0.4282</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0674</v>
+        <v>0.1927</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.7692</v>
+        <v>-0.2759</v>
       </c>
       <c r="O3" t="n">
-        <v>0.8366</v>
+        <v>0.4685</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6959</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.6237</v>
+        <v>-2.5515</v>
       </c>
       <c r="R3" t="n">
-        <v>2.3195</v>
+        <v>1.6237</v>
       </c>
       <c r="S3" t="n">
-        <v>3.5706</v>
+        <v>0.9847</v>
       </c>
       <c r="T3" t="n">
-        <v>3.409</v>
+        <v>0.4641</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1617</v>
+        <v>0.5206</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9304</v>
+        <v>2.2862</v>
       </c>
       <c r="W3" t="n">
-        <v>1.0722</v>
+        <v>2.2862</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. WRIGHT</t>
+          <t>I. BRAZDEIKIS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>6.9557</v>
+        <v>5.2251</v>
       </c>
       <c r="E4" t="n">
-        <v>4.2828</v>
+        <v>3.6857</v>
       </c>
       <c r="F4" t="n">
-        <v>2.673</v>
+        <v>1.5394</v>
       </c>
       <c r="G4" t="n">
-        <v>4.4692</v>
+        <v>3.0708</v>
       </c>
       <c r="H4" t="n">
-        <v>3.5725</v>
+        <v>2.8232</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8968</v>
+        <v>0.2476</v>
       </c>
       <c r="J4" t="n">
-        <v>4.2766</v>
+        <v>3.5715</v>
       </c>
       <c r="K4" t="n">
-        <v>3.8483</v>
+        <v>3.2671</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4282</v>
+        <v>0.3044</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1927</v>
+        <v>-0.5007</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2759</v>
+        <v>-0.4439</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4685</v>
+        <v>-0.0568</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.9278</v>
+        <v>1.6237</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.5515</v>
+        <v>-0.232</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6237</v>
+        <v>1.8556</v>
       </c>
       <c r="S4" t="n">
-        <v>1.1281</v>
+        <v>0.5306999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2715</v>
+        <v>0.3462</v>
       </c>
       <c r="U4" t="n">
-        <v>0.8566</v>
+        <v>0.1845</v>
       </c>
       <c r="V4" t="n">
-        <v>2.2862</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>2.2862</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>I. BRAZDEIKIS</t>
+          <t>E. ULANOVAS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5.0907</v>
+        <v>5.2009</v>
       </c>
       <c r="E5" t="n">
-        <v>3.6857</v>
+        <v>2.9286</v>
       </c>
       <c r="F5" t="n">
-        <v>1.405</v>
+        <v>2.2723</v>
       </c>
       <c r="G5" t="n">
-        <v>3.0708</v>
+        <v>1.8331</v>
       </c>
       <c r="H5" t="n">
-        <v>2.8232</v>
+        <v>-0.2917</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2476</v>
+        <v>2.1248</v>
       </c>
       <c r="J5" t="n">
-        <v>3.5715</v>
+        <v>1.7657</v>
       </c>
       <c r="K5" t="n">
-        <v>3.2671</v>
+        <v>0.4775</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3044</v>
+        <v>1.2882</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5007</v>
+        <v>0.0674</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4439</v>
+        <v>-0.7692</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0568</v>
+        <v>0.8366</v>
       </c>
       <c r="P5" t="n">
-        <v>1.6237</v>
+        <v>0.6959</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.232</v>
+        <v>-1.6237</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8556</v>
+        <v>2.3195</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3962</v>
+        <v>1.7416</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3462</v>
+        <v>1.7144</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0501</v>
+        <v>0.0272</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.9304</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.8743</v>
+        <v>4.0025</v>
       </c>
       <c r="E6" t="n">
-        <v>3.8995</v>
+        <v>4.7252</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.0251</v>
+        <v>-0.7227</v>
       </c>
       <c r="G6" t="n">
         <v>5.9099</v>
@@ -922,13 +922,13 @@
         <v>1.6237</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5021</v>
+        <v>0.626</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4402</v>
+        <v>0.3855</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0619</v>
+        <v>0.2405</v>
       </c>
       <c r="V6" t="n">
         <v>-0.6778999999999999</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. SLEVA</t>
+          <t>N. WILLIAMS-GOSS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.6596</v>
+        <v>2.5959</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3087</v>
+        <v>0.4194</v>
       </c>
       <c r="F7" t="n">
-        <v>2.3508</v>
+        <v>2.1765</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.5301</v>
+        <v>2.1308</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.9842</v>
+        <v>1.0333</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.5459</v>
+        <v>1.0975</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.7361</v>
+        <v>2.3992</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1211</v>
+        <v>1.4557</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.8572</v>
+        <v>0.9435</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.7941</v>
+        <v>-0.2683</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.1053</v>
+        <v>-0.4223</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3113</v>
+        <v>0.154</v>
       </c>
       <c r="P7" t="n">
-        <v>1.6237</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.232</v>
+        <v>-2.7834</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8556</v>
+        <v>2.3195</v>
       </c>
       <c r="S7" t="n">
-        <v>3.1717</v>
+        <v>0.5346</v>
       </c>
       <c r="T7" t="n">
-        <v>2.135</v>
+        <v>0.2675</v>
       </c>
       <c r="U7" t="n">
-        <v>1.0368</v>
+        <v>0.2671</v>
       </c>
       <c r="V7" t="n">
         <v>0.3943</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1418</v>
+        <v>0.5361</v>
       </c>
       <c r="X7" t="n">
-        <v>0.2525</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.5505</v>
+        <v>2.567</v>
       </c>
       <c r="E8" t="n">
-        <v>3.3123</v>
+        <v>3.1944</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7618</v>
+        <v>-0.6274</v>
       </c>
       <c r="G8" t="n">
         <v>2.3293</v>
@@ -1078,13 +1078,13 @@
         <v>0.232</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6361</v>
+        <v>0.6526</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7863</v>
+        <v>0.6684</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1502</v>
+        <v>-0.0158</v>
       </c>
       <c r="V8" t="n">
         <v>-0.6468</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>N. WILLIAMS-GOSS</t>
+          <t>D. SLEVA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>2.0226</v>
+        <v>1.9861</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2883</v>
+        <v>-0.1631</v>
       </c>
       <c r="F9" t="n">
-        <v>2.3109</v>
+        <v>2.1492</v>
       </c>
       <c r="G9" t="n">
-        <v>2.1308</v>
+        <v>-2.5301</v>
       </c>
       <c r="H9" t="n">
-        <v>1.0333</v>
+        <v>-0.9842</v>
       </c>
       <c r="I9" t="n">
-        <v>1.0975</v>
+        <v>-1.5459</v>
       </c>
       <c r="J9" t="n">
-        <v>2.3992</v>
+        <v>-1.7361</v>
       </c>
       <c r="K9" t="n">
-        <v>1.4557</v>
+        <v>0.1211</v>
       </c>
       <c r="L9" t="n">
-        <v>0.9435</v>
+        <v>-1.8572</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2683</v>
+        <v>-0.7941</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4223</v>
+        <v>-1.1053</v>
       </c>
       <c r="O9" t="n">
-        <v>0.154</v>
+        <v>0.3113</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.4639</v>
+        <v>1.6237</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.7834</v>
+        <v>-0.232</v>
       </c>
       <c r="R9" t="n">
-        <v>2.3195</v>
+        <v>1.8556</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0387</v>
+        <v>2.4983</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4402</v>
+        <v>1.6632</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4015</v>
+        <v>0.8351</v>
       </c>
       <c r="V9" t="n">
         <v>0.3943</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5361</v>
+        <v>0.1418</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1418</v>
+        <v>0.2525</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. TUBELIS</t>
+          <t>D. SIRVYDIS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.215</v>
+        <v>1.2319</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7519</v>
+        <v>1.534</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4631</v>
+        <v>-0.3021</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6075</v>
+        <v>1.2909</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6877</v>
+        <v>1.9735</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0803</v>
+        <v>-0.6826</v>
       </c>
       <c r="J10" t="n">
-        <v>1.5655</v>
+        <v>1.0622</v>
       </c>
       <c r="K10" t="n">
-        <v>1.3815</v>
+        <v>1.8485</v>
       </c>
       <c r="L10" t="n">
-        <v>0.184</v>
+        <v>-0.7863</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.9581</v>
+        <v>0.2287</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6938</v>
+        <v>0.1249</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2643</v>
+        <v>0.1038</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.1598</v>
+        <v>0.4639</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1598</v>
+        <v>0.4639</v>
       </c>
       <c r="S10" t="n">
-        <v>1.7673</v>
+        <v>0.5493</v>
       </c>
       <c r="T10" t="n">
-        <v>1.5059</v>
+        <v>0.4718</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2614</v>
+        <v>0.0775</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. SIRVYDIS</t>
+          <t>A. BUTKEVICIUS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7191</v>
+        <v>1.0244</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9875</v>
+        <v>-0.5934</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2685</v>
+        <v>1.6178</v>
       </c>
       <c r="G11" t="n">
-        <v>1.2909</v>
+        <v>0.4859</v>
       </c>
       <c r="H11" t="n">
-        <v>1.9735</v>
+        <v>-0.2904</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6826</v>
+        <v>0.7763</v>
       </c>
       <c r="J11" t="n">
-        <v>1.0622</v>
+        <v>0.5505</v>
       </c>
       <c r="K11" t="n">
-        <v>1.8485</v>
+        <v>0.4033</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.7863</v>
+        <v>0.1472</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2287</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1249</v>
+        <v>-0.6938</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1038</v>
+        <v>0.6291</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4639</v>
+        <v>-0.232</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-1.3917</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4639</v>
+        <v>1.1598</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0365</v>
+        <v>0.7705</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0747</v>
+        <v>0.2478</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1111</v>
+        <v>0.5228</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. BUTKEVICIUS</t>
+          <t>A. TUBELIS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,58 +1345,58 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5526</v>
+        <v>0.4394</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.0652</v>
+        <v>-0.1917</v>
       </c>
       <c r="F12" t="n">
-        <v>1.6178</v>
+        <v>0.6311</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4859</v>
+        <v>0.6075</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.2904</v>
+        <v>0.6877</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7763</v>
+        <v>-0.0803</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5505</v>
+        <v>1.5655</v>
       </c>
       <c r="K12" t="n">
-        <v>0.4033</v>
+        <v>1.3815</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1472</v>
+        <v>0.184</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.06469999999999999</v>
+        <v>-0.9581</v>
       </c>
       <c r="N12" t="n">
         <v>-0.6938</v>
       </c>
       <c r="O12" t="n">
-        <v>0.6291</v>
+        <v>-0.2643</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.232</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.3917</v>
+        <v>-2.3195</v>
       </c>
       <c r="R12" t="n">
         <v>1.1598</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2987</v>
+        <v>0.9917</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.224</v>
+        <v>0.5623</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5228</v>
+        <v>0.4294</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.8062</v>
+        <v>-2.0917</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.7602</v>
+        <v>-3.2137</v>
       </c>
       <c r="F13" t="n">
-        <v>0.954</v>
+        <v>1.122</v>
       </c>
       <c r="G13" t="n">
         <v>-0.7481</v>
@@ -1468,13 +1468,13 @@
         <v>0.6959</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2025</v>
+        <v>0.512</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0747</v>
+        <v>0.4718</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1278</v>
+        <v>0.0402</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>36.4484</v>
+        <v>36.8218</v>
       </c>
       <c r="E14" t="n">
-        <v>21.2972</v>
+        <v>21.6707</v>
       </c>
       <c r="F14" t="n">
-        <v>15.1513</v>
+        <v>15.1511</v>
       </c>
       <c r="G14" t="n">
         <v>22.9484</v>
@@ -1516,7 +1516,7 @@
         <v>13.2283</v>
       </c>
       <c r="I14" t="n">
-        <v>9.7202</v>
+        <v>9.720199999999998</v>
       </c>
       <c r="J14" t="n">
         <v>25.472</v>
@@ -1537,7 +1537,7 @@
         <v>3.3804</v>
       </c>
       <c r="P14" t="n">
-        <v>9.999999999998899e-05</v>
+        <v>9.99999999995449e-05</v>
       </c>
       <c r="Q14" t="n">
         <v>-17.3966</v>
@@ -1546,13 +1546,13 @@
         <v>17.3966</v>
       </c>
       <c r="S14" t="n">
-        <v>11.8917</v>
+        <v>12.2652</v>
       </c>
       <c r="T14" t="n">
-        <v>7.6877</v>
+        <v>8.061199999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>4.204300000000001</v>
+        <v>4.2041</v>
       </c>
       <c r="V14" t="n">
         <v>1.6083</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1925</v>
+        <v>-0.1043</v>
       </c>
       <c r="E15" t="n">
-        <v>2.7335</v>
+        <v>2.6155</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.541</v>
+        <v>-2.7198</v>
       </c>
       <c r="G15" t="n">
         <v>1.2134</v>
@@ -1624,13 +1624,13 @@
         <v>1.8556</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5544</v>
+        <v>-0.8511</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0474</v>
+        <v>-0.07049999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6018</v>
+        <v>-0.7806</v>
       </c>
       <c r="V15" t="n">
         <v>-0.9304</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. PARKER</t>
+          <t>V. MARINKOVIC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-2.088</v>
+        <v>-1.9901</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.1408</v>
+        <v>-0.8552</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0528</v>
+        <v>-1.1348</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.5869</v>
+        <v>-0.9375</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.7274</v>
+        <v>-1.0346</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1406</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.6823</v>
+        <v>1.3147</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.7191</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0368</v>
+        <v>0.6257</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.9045</v>
+        <v>-2.2522</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.0083</v>
+        <v>-1.7236</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1038</v>
+        <v>-0.5286</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.232</v>
+        <v>0.232</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1598</v>
+        <v>-1.3917</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9278</v>
+        <v>1.6237</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1274</v>
+        <v>-1.2845</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2987</v>
+        <v>-0.7782</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1713</v>
+        <v>-0.5063</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>V. MARINKOVIC</t>
+          <t>J. PARKER</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.2761</v>
+        <v>-2.0373</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.9732</v>
+        <v>-2.0228</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.3029</v>
+        <v>-0.0144</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.9375</v>
+        <v>-1.5869</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.0346</v>
+        <v>-1.7274</v>
       </c>
       <c r="I17" t="n">
-        <v>0.09710000000000001</v>
+        <v>0.1406</v>
       </c>
       <c r="J17" t="n">
-        <v>1.3147</v>
+        <v>-0.6823</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6889999999999999</v>
+        <v>-0.7191</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6257</v>
+        <v>0.0368</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.2522</v>
+        <v>-0.9045</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.7236</v>
+        <v>-1.0083</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.5286</v>
+        <v>0.1038</v>
       </c>
       <c r="P17" t="n">
-        <v>0.232</v>
+        <v>-0.232</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.3917</v>
+        <v>-1.1598</v>
       </c>
       <c r="R17" t="n">
-        <v>1.6237</v>
+        <v>0.9278</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.5705</v>
+        <v>-0.0767</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8962</v>
+        <v>-0.1808</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6743</v>
+        <v>0.1041</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.4118</v>
+        <v>-2.5462</v>
       </c>
       <c r="E18" t="n">
         <v>0.0157</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.4274</v>
+        <v>-2.5618</v>
       </c>
       <c r="G18" t="n">
         <v>-0.6159</v>
@@ -1858,13 +1858,13 @@
         <v>1.8556</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.1</v>
+        <v>-1.2344</v>
       </c>
       <c r="T18" t="n">
         <v>-0.0272</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.0728</v>
+        <v>-1.2072</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,10 +1891,10 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.8318</v>
+        <v>-4.3036</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4567</v>
+        <v>-1.9285</v>
       </c>
       <c r="F19" t="n">
         <v>-2.3751</v>
@@ -1936,10 +1936,10 @@
         <v>1.6237</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5149</v>
+        <v>-0.9867</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1019</v>
+        <v>-0.5737</v>
       </c>
       <c r="U19" t="n">
         <v>-0.4129</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.7149</v>
+        <v>-4.4232</v>
       </c>
       <c r="E20" t="n">
         <v>-3.0133</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.7016</v>
+        <v>-1.4099</v>
       </c>
       <c r="G20" t="n">
         <v>-3.1403</v>
@@ -2014,13 +2014,13 @@
         <v>1.8556</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.5024</v>
+        <v>-1.2107</v>
       </c>
       <c r="T20" t="n">
         <v>-1.0376</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4648</v>
+        <v>-0.1731</v>
       </c>
       <c r="V20" t="n">
         <v>-0.5361</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.3377</v>
+        <v>-5.9553</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.2921</v>
+        <v>-1.9998</v>
       </c>
       <c r="F21" t="n">
-        <v>-4.0455</v>
+        <v>-3.9555</v>
       </c>
       <c r="G21" t="n">
         <v>-4.3939</v>
@@ -2092,13 +2092,13 @@
         <v>2.7834</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.3381</v>
+        <v>-1.9558</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2442</v>
+        <v>-0.4635</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.5823</v>
+        <v>-1.4923</v>
       </c>
       <c r="V21" t="n">
         <v>0.3943</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.9036</v>
+        <v>-6.2409</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.2489</v>
+        <v>-2.7771</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.6548</v>
+        <v>-3.4639</v>
       </c>
       <c r="G22" t="n">
         <v>-1.6787</v>
@@ -2170,13 +2170,13 @@
         <v>2.0876</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.2971</v>
+        <v>-1.6344</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8804</v>
+        <v>-0.4086</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.4167</v>
+        <v>-1.2259</v>
       </c>
       <c r="V22" t="n">
         <v>-1.0722</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-9.077199999999999</v>
+        <v>-8.061299999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.8476</v>
+        <v>-6.2579</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.2296</v>
+        <v>-1.8035</v>
       </c>
       <c r="G23" t="n">
         <v>-8.4247</v>
@@ -2248,13 +2248,13 @@
         <v>2.7834</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.8871</v>
+        <v>-1.8712</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.2538</v>
+        <v>-0.664</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.6333</v>
+        <v>-1.2072</v>
       </c>
       <c r="V23" t="n">
         <v>2.0026</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-36.4486</v>
+        <v>-35.6622</v>
       </c>
       <c r="E24" t="n">
         <v>-16.2234</v>
       </c>
       <c r="F24" t="n">
-        <v>-20.2251</v>
+        <v>-19.4387</v>
       </c>
       <c r="G24" t="n">
         <v>-22.9484</v>
@@ -2299,7 +2299,7 @@
         <v>-9.720000000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>2.523799999999999</v>
+        <v>2.5238</v>
       </c>
       <c r="K24" t="n">
         <v>5.904</v>
@@ -2317,7 +2317,7 @@
         <v>-6.339700000000001</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.775557561562891e-17</v>
       </c>
       <c r="Q24" t="n">
         <v>-17.3965</v>
@@ -2326,13 +2326,13 @@
         <v>17.3964</v>
       </c>
       <c r="S24" t="n">
-        <v>-11.8919</v>
+        <v>-11.1055</v>
       </c>
       <c r="T24" t="n">
-        <v>-4.2042</v>
+        <v>-4.2041</v>
       </c>
       <c r="U24" t="n">
-        <v>-7.6876</v>
+        <v>-6.9014</v>
       </c>
       <c r="V24" t="n">
         <v>-1.6083</v>
